--- a/data/trans_orig/Q57-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Estudios-trans_orig.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la autopercepción de felicidad</t>
+          <t>Puntuación media de la autopercepción de felicidad (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,37</t>
+          <t>7,11; 7,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,54</t>
+          <t>7,19; 7,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 6,91</t>
+          <t>6,66; 6,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,13</t>
+          <t>6,87; 7,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,08</t>
+          <t>6,9; 7,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,25</t>
+          <t>7,05; 7,26</t>
         </is>
       </c>
     </row>
@@ -711,32 +711,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 7,82</t>
+          <t>7,69; 7,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 8,56</t>
+          <t>8,25; 8,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 7,7</t>
+          <t>7,56; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,15</t>
+          <t>7,74; 8,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,74</t>
+          <t>7,65; 7,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 8,33</t>
+          <t>8,04; 8,31</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 8,17</t>
+          <t>7,95; 8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 8,43</t>
+          <t>8,18; 8,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 8,11</t>
+          <t>7,9; 8,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,11</t>
+          <t>7,95; 8,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 8,36</t>
+          <t>8,2; 8,36</t>
         </is>
       </c>
     </row>
@@ -876,27 +876,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,38</t>
+          <t>8,12; 8,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,51</t>
+          <t>7,4; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 7,93</t>
+          <t>7,72; 7,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,61</t>
+          <t>7,53; 7,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,12</t>
+          <t>7,94; 8,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q57-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Estudios-trans_orig.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,36</t>
+          <t>7,12; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,55</t>
+          <t>7,25; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 6,93</t>
+          <t>6,65; 6,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,13</t>
+          <t>6,86; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,08</t>
+          <t>6,89; 7,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,26</t>
+          <t>7,06; 7,26</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -716,27 +716,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 8,56</t>
+          <t>8,19; 8,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,7</t>
+          <t>7,57; 7,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 8,15</t>
+          <t>8,07; 8,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,75</t>
+          <t>7,65; 7,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 8,31</t>
+          <t>8,15; 8,24</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>8,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -791,32 +791,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,18</t>
+          <t>7,94; 8,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 8,42</t>
+          <t>8,17; 8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 8,1</t>
+          <t>7,89; 8,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 8,35</t>
+          <t>8,15; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,1</t>
+          <t>7,94; 8,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 8,36</t>
+          <t>8,2; 8,35</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>8,02</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,41</t>
+          <t>8,08; 8,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,51</t>
+          <t>7,39; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 7,94</t>
+          <t>7,85; 7,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,13</t>
+          <t>7,98; 8,05</t>
         </is>
       </c>
     </row>
